--- a/output/StructureDefinition-t-cabs-observation-ti.xlsx
+++ b/output/StructureDefinition-t-cabs-observation-ti.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-20T17:13:04+01:00</t>
+    <t>2025-11-21T13:42:11+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-t-cabs-observation-ti.xlsx
+++ b/output/StructureDefinition-t-cabs-observation-ti.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-25T10:29:35+01:00</t>
+    <t>2025-12-09T09:55:43+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-t-cabs-observation-ti.xlsx
+++ b/output/StructureDefinition-t-cabs-observation-ti.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5275" uniqueCount="738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5275" uniqueCount="739">
   <si>
     <t>Property</t>
   </si>
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://t-cabs.org/StructureDefinition/t-cabs-observation-ti</t>
+    <t>https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-observation-ti</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-09T09:55:43+01:00</t>
+    <t>2026-02-19T13:21:58+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://t-cabs.org/StructureDefinition/t-cabs-observation-beatmungsparameter</t>
+    <t>https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-observation-beatmungsparameter</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -716,7 +716,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://t-cabs.org/StructureDefinition/t-cabs-procedure-beatmung)
+    <t xml:space="preserve">Reference(https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-procedure-beatmung)
 </t>
   </si>
   <si>
@@ -878,7 +878,7 @@
     <t>Code defined by a terminology system</t>
   </si>
   <si>
-    <t>A reference to a code defined by a terminology system.</t>
+    <t>Duration of the inflation phase if time-terminated.</t>
   </si>
   <si>
     <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
@@ -1062,7 +1062,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://t-cabs.org/StructureDefinition/t-cabs-patient)
+    <t xml:space="preserve">Reference(https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-patient)
 </t>
   </si>
   <si>
@@ -1822,6 +1822,9 @@
     <t>Observation.bodySite.coding</t>
   </si>
   <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
     <t>Observation.bodySite.coding.id</t>
   </si>
   <si>
@@ -1913,7 +1916,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://t-cabs.org/StructureDefinition/t-cabs-devicemetric-numericmetric)
+    <t xml:space="preserve">Reference(https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-devicemetric-numericmetric)
 </t>
   </si>
   <si>
@@ -13221,7 +13224,7 @@
         <v>274</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>275</v>
+        <v>581</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>276</v>
@@ -13317,10 +13320,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13441,10 +13444,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13567,10 +13570,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13672,7 +13675,7 @@
         <v>84</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>84</v>
@@ -13695,10 +13698,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13798,7 +13801,7 @@
         <v>84</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>84</v>
@@ -13821,10 +13824,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13924,7 +13927,7 @@
         <v>84</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>84</v>
@@ -13947,10 +13950,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14073,10 +14076,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14201,10 +14204,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14329,10 +14332,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14358,16 +14361,16 @@
         <v>245</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>84</v>
@@ -14395,10 +14398,10 @@
         <v>162</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>84</v>
@@ -14416,7 +14419,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14443,10 +14446,10 @@
         <v>84</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>84</v>
@@ -14457,10 +14460,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14483,16 +14486,16 @@
         <v>84</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -14542,7 +14545,7 @@
         <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14566,27 +14569,27 @@
         <v>84</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR94" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14609,16 +14612,16 @@
         <v>84</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14668,7 +14671,7 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14692,27 +14695,27 @@
         <v>84</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR95" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14735,19 +14738,19 @@
         <v>84</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>84</v>
@@ -14796,7 +14799,7 @@
         <v>84</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14808,7 +14811,7 @@
         <v>84</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>84</v>
@@ -14823,10 +14826,10 @@
         <v>84</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>84</v>
@@ -14837,10 +14840,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14961,10 +14964,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15087,14 +15090,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -15116,10 +15119,10 @@
         <v>116</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>119</v>
@@ -15174,7 +15177,7 @@
         <v>84</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15215,10 +15218,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15241,13 +15244,13 @@
         <v>84</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15298,7 +15301,7 @@
         <v>84</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>82</v>
@@ -15307,16 +15310,16 @@
         <v>95</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>84</v>
@@ -15325,10 +15328,10 @@
         <v>84</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>84</v>
@@ -15339,10 +15342,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15463,10 +15466,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15589,10 +15592,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15717,10 +15720,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15749,7 +15752,7 @@
         <v>458</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
@@ -15845,10 +15848,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15971,10 +15974,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16097,10 +16100,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16225,10 +16228,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16251,13 +16254,13 @@
         <v>84</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -16308,7 +16311,7 @@
         <v>84</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>82</v>
@@ -16317,16 +16320,16 @@
         <v>95</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>84</v>
@@ -16335,10 +16338,10 @@
         <v>84</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AQ108" t="s" s="2">
         <v>84</v>
@@ -16349,10 +16352,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16473,10 +16476,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16599,10 +16602,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16727,10 +16730,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16759,7 +16762,7 @@
         <v>458</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
@@ -16855,10 +16858,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16981,10 +16984,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17107,10 +17110,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17235,10 +17238,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17264,16 +17267,16 @@
         <v>245</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>84</v>
@@ -17283,7 +17286,7 @@
         <v>84</v>
       </c>
       <c r="S116" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="T116" t="s" s="2">
         <v>84</v>
@@ -17301,10 +17304,10 @@
         <v>176</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>84</v>
@@ -17322,7 +17325,7 @@
         <v>84</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>82</v>
@@ -17346,10 +17349,10 @@
         <v>84</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AP116" t="s" s="2">
         <v>558</v>
@@ -17363,10 +17366,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17392,16 +17395,16 @@
         <v>245</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>84</v>
@@ -17429,10 +17432,10 @@
         <v>162</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>84</v>
@@ -17450,7 +17453,7 @@
         <v>84</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>82</v>
@@ -17474,10 +17477,10 @@
         <v>84</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AP117" t="s" s="2">
         <v>558</v>
@@ -17491,10 +17494,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17517,17 +17520,17 @@
         <v>84</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>84</v>
@@ -17576,7 +17579,7 @@
         <v>84</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>82</v>
@@ -17606,7 +17609,7 @@
         <v>84</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AQ118" t="s" s="2">
         <v>84</v>
@@ -17617,10 +17620,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17646,10 +17649,10 @@
         <v>109</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -17700,7 +17703,7 @@
         <v>84</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>82</v>
@@ -17727,10 +17730,10 @@
         <v>84</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AQ119" t="s" s="2">
         <v>84</v>
@@ -17741,10 +17744,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17767,16 +17770,16 @@
         <v>96</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -17826,7 +17829,7 @@
         <v>84</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>82</v>
@@ -17853,10 +17856,10 @@
         <v>84</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AP120" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AQ120" t="s" s="2">
         <v>84</v>
@@ -17867,10 +17870,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17893,16 +17896,16 @@
         <v>96</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -17952,7 +17955,7 @@
         <v>84</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>82</v>
@@ -17979,10 +17982,10 @@
         <v>84</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AP121" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AQ121" t="s" s="2">
         <v>84</v>
@@ -17993,10 +17996,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18019,19 +18022,19 @@
         <v>96</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>84</v>
@@ -18080,7 +18083,7 @@
         <v>84</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>82</v>
@@ -18107,10 +18110,10 @@
         <v>84</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AQ122" t="s" s="2">
         <v>84</v>
@@ -18121,10 +18124,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18245,10 +18248,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18371,14 +18374,14 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -18400,10 +18403,10 @@
         <v>116</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="N125" t="s" s="2">
         <v>119</v>
@@ -18458,7 +18461,7 @@
         <v>84</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>82</v>
@@ -18499,10 +18502,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18528,13 +18531,13 @@
         <v>245</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="O126" t="s" s="2">
         <v>263</v>
@@ -18565,10 +18568,10 @@
         <v>162</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>84</v>
@@ -18586,7 +18589,7 @@
         <v>84</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>95</v>
@@ -18610,7 +18613,7 @@
         <v>84</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>267</v>
@@ -18627,10 +18630,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18653,16 +18656,16 @@
         <v>96</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="M127" t="s" s="2">
         <v>428</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="O127" t="s" s="2">
         <v>430</v>
@@ -18714,7 +18717,7 @@
         <v>84</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>82</v>
@@ -18738,7 +18741,7 @@
         <v>84</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>433</v>
@@ -18755,10 +18758,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18784,13 +18787,13 @@
         <v>245</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="O128" t="s" s="2">
         <v>543</v>
@@ -18842,7 +18845,7 @@
         <v>84</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>82</v>
@@ -18851,7 +18854,7 @@
         <v>95</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>107</v>
@@ -18883,10 +18886,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18949,28 +18952,28 @@
         <v>153</v>
       </c>
       <c r="Y129" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF129" t="s" s="2">
         <v>733</v>
-      </c>
-      <c r="Z129" t="s" s="2">
-        <v>734</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>732</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>82</v>
@@ -19011,10 +19014,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19040,16 +19043,16 @@
         <v>85</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>84</v>
@@ -19098,7 +19101,7 @@
         <v>84</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>82</v>
@@ -19125,10 +19128,10 @@
         <v>84</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AQ130" t="s" s="2">
         <v>84</v>
